--- a/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.N_00155_18880712/oocihm.N_00155_18880712.4.xlsx
+++ b/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.N_00155_18880712/oocihm.N_00155_18880712.4.xlsx
@@ -464,12 +464,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - paddle</t>
+          <t>Possible duplicate lines - paddle</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - abbyy</t>
+          <t>Possible duplicate lines - abbyy</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -983,7 +983,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap issue count</t>
+          <t>Possible duplicate lines issue count</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">

--- a/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.N_00155_18880712/oocihm.N_00155_18880712.4.xlsx
+++ b/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.N_00155_18880712/oocihm.N_00155_18880712.4.xlsx
@@ -416,14 +416,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y47"/>
+  <dimension ref="A1:Y32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
     <col width="60" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="60" customWidth="1" min="6" max="6"/>
     <col width="60" customWidth="1" min="7" max="7"/>
     <col width="60" customWidth="1" min="8" max="8"/>
@@ -431,7 +431,7 @@
     <col width="60" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="31" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
     <col width="60" customWidth="1" min="14" max="14"/>
     <col width="38" customWidth="1" min="15" max="15"/>
     <col width="60" customWidth="1" min="16" max="16"/>
@@ -617,19 +617,23 @@
       </c>
       <c r="J2" s="1" t="inlineStr">
         <is>
-          <t>L256: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR, U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: ç¦�</t>
+          <t>L256: stray/suspicious non-ASCII glyph(s): U+798F CJK UNIFIED IDEOGRAPH-798F | isolated marker/symbol line :: 福</t>
         </is>
       </c>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>L66: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: 65 &amp; â€¢ | primary effect of free trade in Canada</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE :: [BOM]THE HAMILTON WEEKLY TIMES, THURSDAY, JULY 12, 1888.</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" s="1" t="inlineStr"/>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE :: [BOM]THE HAMILTON WEEKLY TIMES, THURSDAY, JULY 12, 1888.</t>
+        </is>
+      </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
-          <t>L256: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR, U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: ç¦�</t>
+          <t>L256: stray/suspicious non-ASCII glyph(s): U+798F CJK UNIFIED IDEOGRAPH-798F | isolated marker/symbol line :: 福</t>
         </is>
       </c>
       <c r="O2" s="1" t="inlineStr">
@@ -685,7 +689,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>809</t>
+          <t>679</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr"/>
@@ -697,7 +701,7 @@
       </c>
       <c r="G3" s="1" t="inlineStr">
         <is>
-          <t>L427: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER | suspicious token(s): 46summer (letter/digit mix) | candidate OCR token mismatch vs other OCR: "summer" vs "46summer" :: battle with 46summer diseaseâ€� must_â€” -</t>
+          <t>L427: suspicious token(s): 46summer (letter/digit mix) | candidate OCR token mismatch vs other OCR: "summer" vs "46summer" :: battle with 46summer disease” must_— -</t>
         </is>
       </c>
       <c r="H3" s="1" t="inlineStr">
@@ -710,14 +714,10 @@
           <t>L63: line starts with digit/letter garbage token | suspicious token(s): 1Set1 (letter/digit mix), 1Ger (letter/digit mix) :: 1Set1.1Ger: imports, and the articles to be exported</t>
         </is>
       </c>
-      <c r="J3" s="1" t="inlineStr">
-        <is>
-          <t>L269: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: other occupations tells the same storyâ€”â€”</t>
-        </is>
-      </c>
+      <c r="J3" s="1" t="inlineStr"/>
       <c r="K3" s="1" t="inlineStr">
         <is>
-          <t>L71: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: repeated periods | line starts with punctuation glued to text :: __________â€” ...............| his produce as such prices as now prevail,</t>
+          <t>L66: stray/suspicious non-ASCII glyph(s): U+2022 BULLET :: 65 &amp; • | primary effect of free trade in Canada</t>
         </is>
       </c>
       <c r="L3" s="1" t="inlineStr"/>
@@ -735,13 +735,13 @@
       </c>
       <c r="Q3" s="1" t="inlineStr">
         <is>
-          <t>L71: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: repeated periods | line starts with punctuation glued to text :: __________â€” ...............| his produce as such prices as now prevail,</t>
+          <t>L71: punctuation artifact: repeated periods | line starts with punctuation glued to text :: __________— ...............| his produce as such prices as now prevail,</t>
         </is>
       </c>
       <c r="R3" s="1" t="inlineStr"/>
       <c r="S3" s="1" t="inlineStr">
         <is>
-          <t>L71: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: repeated periods | line starts with punctuation glued to text :: __________â€” ...............| his produce as such prices as now prevail,</t>
+          <t>L71: punctuation artifact: repeated periods | line starts with punctuation glued to text :: __________— ...............| his produce as such prices as now prevail,</t>
         </is>
       </c>
       <c r="T3" s="1" t="inlineStr"/>
@@ -784,7 +784,7 @@
       </c>
       <c r="G4" s="1" t="inlineStr">
         <is>
-          <t>L429: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN | suspicious token(s): 1The (letter/digit mix) | localized OCR phrase divergence vs other OCR: "disease" vs "1The Fiftieth Day of Zachar s Fast" :: -1The Fiftieth Day of Zacharâ€™s Fast.</t>
+          <t>L429: suspicious token(s): 1The (letter/digit mix) | localized OCR phrase divergence vs other OCR: "disease" vs "1The Fiftieth Day of Zachar’s Fast" :: -1The Fiftieth Day of Zachar’s Fast.</t>
         </is>
       </c>
       <c r="H4" s="1" t="inlineStr">
@@ -797,14 +797,10 @@
           <t>L65: suspicious token(s): AecRIO (odd internal casing) :: Ohe AecRIO CANNES, can only be produced by labor. The</t>
         </is>
       </c>
-      <c r="J4" s="1" t="inlineStr">
-        <is>
-          <t>L838: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€” A golden wedding is raro enough, but</t>
-        </is>
-      </c>
+      <c r="J4" s="1" t="inlineStr"/>
       <c r="K4" s="1" t="inlineStr">
         <is>
-          <t>L78: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: not better off.â€”Hamilton Spectator.-</t>
+          <t>L111: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | punctuation artifact: repeated periods :: •....,trade would raise wages in Canada, just as</t>
         </is>
       </c>
       <c r="L4" s="1" t="inlineStr"/>
@@ -850,12 +846,12 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>27</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>54</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr"/>
@@ -863,7 +859,7 @@
       <c r="F5" s="1" t="inlineStr"/>
       <c r="G5" s="1" t="inlineStr">
         <is>
-          <t>L713: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN | line starts with punctuation glued to text | suspicious token(s): 1I (letter/digit mix) | localized OCR phrase divergence vs other OCR: "" vs "1I" :: -__1I Hoffman Club, on Clevelandâ€™s re-election,</t>
+          <t>L713: line starts with punctuation glued to text | suspicious token(s): 1I (letter/digit mix) | localized OCR phrase divergence vs other OCR: "" vs "1I" :: -__1I Hoffman Club, on Cleveland’s re-election,</t>
         </is>
       </c>
       <c r="H5" s="1" t="inlineStr">
@@ -879,7 +875,7 @@
       <c r="J5" s="1" t="inlineStr"/>
       <c r="K5" s="1" t="inlineStr">
         <is>
-          <t>L87: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+02DC SMALL TILDE | punctuation artifact: repeated periods :: ..â€˜.%.3 cottons, etc., and the result would be a</t>
+          <t>L125: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | punctuation artifact: repeated periods :: duties simply caused prices of commod-f...•.</t>
         </is>
       </c>
       <c r="L5" s="1" t="inlineStr"/>
@@ -950,7 +946,7 @@
       <c r="J6" s="1" t="inlineStr"/>
       <c r="K6" s="1" t="inlineStr">
         <is>
-          <t>L109: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: they contend that free trade would increase |â€ž 3</t>
+          <t>L456: stray/suspicious non-ASCII glyph(s): U+2022 BULLET :: of the Church of Scotland, gives various |__•___________</t>
         </is>
       </c>
       <c r="L6" s="1" t="inlineStr"/>
@@ -964,7 +960,7 @@
       <c r="P6" s="1" t="inlineStr"/>
       <c r="Q6" s="1" t="inlineStr">
         <is>
-          <t>L87: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+02DC SMALL TILDE | punctuation artifact: repeated periods :: ..â€˜.%.3 cottons, etc., and the result would be a</t>
+          <t>L87: punctuation artifact: repeated periods :: ..‘.%.3 cottons, etc., and the result would be a</t>
         </is>
       </c>
       <c r="R6" s="1" t="inlineStr"/>
@@ -1007,13 +1003,13 @@
       </c>
       <c r="I7" s="1" t="inlineStr">
         <is>
-          <t>L427: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER | suspicious token(s): 46summer (letter/digit mix) | candidate OCR token mismatch vs other OCR: "summer" vs "46summer" :: battle with 46summer diseaseâ€� must_â€” -</t>
+          <t>L427: suspicious token(s): 46summer (letter/digit mix) | candidate OCR token mismatch vs other OCR: "summer" vs "46summer" :: battle with 46summer disease” must_— -</t>
         </is>
       </c>
       <c r="J7" s="1" t="inlineStr"/>
       <c r="K7" s="1" t="inlineStr">
         <is>
-          <t>L111: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | punctuation artifact: repeated periods :: â€¢....,trade would raise wages in Canada, just as</t>
+          <t>L734: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | punctuation artifact: double/multiple hyphen; hyphen/bullet debris :: 2— ----------------•——— --------| employer, Mr. Alfred Nicholson, farmer, of</t>
         </is>
       </c>
       <c r="L7" s="1" t="inlineStr"/>
@@ -1033,7 +1029,7 @@
       <c r="R7" s="1" t="inlineStr"/>
       <c r="S7" s="1" t="inlineStr">
         <is>
-          <t>L709: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | line starts with punctuation glued to text :: -__________________â€”____________| Mahoney, a retired bookmaker, bet $20,000</t>
+          <t>L709: line starts with punctuation glued to text :: -__________________—____________| Mahoney, a retired bookmaker, bet $20,000</t>
         </is>
       </c>
       <c r="T7" s="1" t="inlineStr"/>
@@ -1070,15 +1066,11 @@
       </c>
       <c r="I8" s="1" t="inlineStr">
         <is>
-          <t>L429: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN | suspicious token(s): 1The (letter/digit mix) | localized OCR phrase divergence vs other OCR: "disease" vs "1The Fiftieth Day of Zachar s Fast" :: -1The Fiftieth Day of Zacharâ€™s Fast.</t>
+          <t>L429: suspicious token(s): 1The (letter/digit mix) | localized OCR phrase divergence vs other OCR: "disease" vs "1The Fiftieth Day of Zachar’s Fast" :: -1The Fiftieth Day of Zachar’s Fast.</t>
         </is>
       </c>
       <c r="J8" s="1" t="inlineStr"/>
-      <c r="K8" s="1" t="inlineStr">
-        <is>
-          <t>L123: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN | punctuation artifact: repeated periods :: ... 3 * , , it ? It hasnâ€™t done anything of the kind</t>
-        </is>
-      </c>
+      <c r="K8" s="1" t="inlineStr"/>
       <c r="L8" s="1" t="inlineStr"/>
       <c r="M8" s="1" t="inlineStr"/>
       <c r="N8" s="1" t="inlineStr">
@@ -1096,7 +1088,7 @@
       <c r="R8" s="1" t="inlineStr"/>
       <c r="S8" s="1" t="inlineStr">
         <is>
-          <t>L713: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN | line starts with punctuation glued to text | suspicious token(s): 1I (letter/digit mix) | localized OCR phrase divergence vs other OCR: "" vs "1I" :: -__1I Hoffman Club, on Clevelandâ€™s re-election,</t>
+          <t>L713: line starts with punctuation glued to text | suspicious token(s): 1I (letter/digit mix) | localized OCR phrase divergence vs other OCR: "" vs "1I" :: -__1I Hoffman Club, on Cleveland’s re-election,</t>
         </is>
       </c>
       <c r="T8" s="1" t="inlineStr"/>
@@ -1137,11 +1129,7 @@
         </is>
       </c>
       <c r="J9" s="1" t="inlineStr"/>
-      <c r="K9" s="1" t="inlineStr">
-        <is>
-          <t>L125: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | punctuation artifact: repeated periods :: duties simply caused prices of commod-f...â€¢.</t>
-        </is>
-      </c>
+      <c r="K9" s="1" t="inlineStr"/>
       <c r="L9" s="1" t="inlineStr"/>
       <c r="M9" s="1" t="inlineStr"/>
       <c r="N9" s="1" t="inlineStr"/>
@@ -1173,12 +1161,12 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr"/>
@@ -1196,11 +1184,7 @@
         </is>
       </c>
       <c r="J10" s="1" t="inlineStr"/>
-      <c r="K10" s="1" t="inlineStr">
-        <is>
-          <t>L176: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: erecting a school south of King street.â€”</t>
-        </is>
-      </c>
+      <c r="K10" s="1" t="inlineStr"/>
       <c r="L10" s="1" t="inlineStr"/>
       <c r="M10" s="1" t="inlineStr"/>
       <c r="N10" s="1" t="inlineStr"/>
@@ -1233,7 +1217,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr"/>
@@ -1247,11 +1231,7 @@
         </is>
       </c>
       <c r="J11" s="1" t="inlineStr"/>
-      <c r="K11" s="1" t="inlineStr">
-        <is>
-          <t>L193: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+02DC SMALL TILDE :: the day, â€˜so great were the fears</t>
-        </is>
-      </c>
+      <c r="K11" s="1" t="inlineStr"/>
       <c r="L11" s="1" t="inlineStr"/>
       <c r="M11" s="1" t="inlineStr"/>
       <c r="N11" s="1" t="inlineStr"/>
@@ -1294,15 +1274,11 @@
       <c r="H12" s="1" t="inlineStr"/>
       <c r="I12" s="1" t="inlineStr">
         <is>
-          <t>L669: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: repeated periods; double/multiple hyphen | suspicious token(s): A1 (letter/digit mix) :: other words, his employment is lesssteady; I.. -------â€” ------A1, ,.</t>
+          <t>L669: punctuation artifact: repeated periods; double/multiple hyphen | suspicious token(s): A1 (letter/digit mix) :: other words, his employment is lesssteady; I.. -------— ------A1, ,.</t>
         </is>
       </c>
       <c r="J12" s="1" t="inlineStr"/>
-      <c r="K12" s="1" t="inlineStr">
-        <is>
-          <t>L195: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: were exercised the entire cropâ€”the back-</t>
-        </is>
-      </c>
+      <c r="K12" s="1" t="inlineStr"/>
       <c r="L12" s="1" t="inlineStr"/>
       <c r="M12" s="1" t="inlineStr"/>
       <c r="N12" s="1" t="inlineStr"/>
@@ -1345,15 +1321,11 @@
       <c r="H13" s="1" t="inlineStr"/>
       <c r="I13" s="1" t="inlineStr">
         <is>
-          <t>L713: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN | line starts with punctuation glued to text | suspicious token(s): 1I (letter/digit mix) | localized OCR phrase divergence vs other OCR: "" vs "1I" :: -__1I Hoffman Club, on Clevelandâ€™s re-election,</t>
+          <t>L713: line starts with punctuation glued to text | suspicious token(s): 1I (letter/digit mix) | localized OCR phrase divergence vs other OCR: "" vs "1I" :: -__1I Hoffman Club, on Cleveland’s re-election,</t>
         </is>
       </c>
       <c r="J13" s="1" t="inlineStr"/>
-      <c r="K13" s="1" t="inlineStr">
-        <is>
-          <t>L196: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: bone of the Stateâ€”would be devoured by</t>
-        </is>
-      </c>
+      <c r="K13" s="1" t="inlineStr"/>
       <c r="L13" s="1" t="inlineStr"/>
       <c r="M13" s="1" t="inlineStr"/>
       <c r="N13" s="1" t="inlineStr"/>
@@ -1361,7 +1333,7 @@
       <c r="P13" s="1" t="inlineStr"/>
       <c r="Q13" s="1" t="inlineStr">
         <is>
-          <t>L111: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | punctuation artifact: repeated periods :: â€¢....,trade would raise wages in Canada, just as</t>
+          <t>L111: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | punctuation artifact: repeated periods :: •....,trade would raise wages in Canada, just as</t>
         </is>
       </c>
       <c r="R13" s="1" t="inlineStr"/>
@@ -1396,15 +1368,11 @@
       <c r="H14" s="1" t="inlineStr"/>
       <c r="I14" s="1" t="inlineStr">
         <is>
-          <t>L714: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN | suspicious token(s): wmNe (odd internal casing) :: by wmNe^Tis molested Mahoneyâ€™s forfeit in case of failure is fixed</t>
+          <t>L714: suspicious token(s): wmNe (odd internal casing) :: by wmNe^Tis molested Mahoney’s forfeit in case of failure is fixed</t>
         </is>
       </c>
       <c r="J14" s="1" t="inlineStr"/>
-      <c r="K14" s="1" t="inlineStr">
-        <is>
-          <t>L317: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: talistsâ€”there should be no second or inter-</t>
-        </is>
-      </c>
+      <c r="K14" s="1" t="inlineStr"/>
       <c r="L14" s="1" t="inlineStr"/>
       <c r="M14" s="1" t="inlineStr"/>
       <c r="N14" s="1" t="inlineStr"/>
@@ -1451,11 +1419,7 @@
         </is>
       </c>
       <c r="J15" s="1" t="inlineStr"/>
-      <c r="K15" s="1" t="inlineStr">
-        <is>
-          <t>L363: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: very careful regarding his statements, but ments, interest not to exceed 6 per cent.â€”</t>
-        </is>
-      </c>
+      <c r="K15" s="1" t="inlineStr"/>
       <c r="L15" s="1" t="inlineStr"/>
       <c r="M15" s="1" t="inlineStr"/>
       <c r="N15" s="1" t="inlineStr"/>
@@ -1463,7 +1427,7 @@
       <c r="P15" s="1" t="inlineStr"/>
       <c r="Q15" s="1" t="inlineStr">
         <is>
-          <t>L123: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN | punctuation artifact: repeated periods :: ... 3 * , , it ? It hasnâ€™t done anything of the kind</t>
+          <t>L123: punctuation artifact: repeated periods :: ... 3 * , , it ? It hasn’t done anything of the kind</t>
         </is>
       </c>
       <c r="R15" s="1" t="inlineStr"/>
@@ -1502,11 +1466,7 @@
         </is>
       </c>
       <c r="J16" s="1" t="inlineStr"/>
-      <c r="K16" s="1" t="inlineStr">
-        <is>
-          <t>L377: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: finished, the cost not to exceed $5,000.â€”</t>
-        </is>
-      </c>
+      <c r="K16" s="1" t="inlineStr"/>
       <c r="L16" s="1" t="inlineStr"/>
       <c r="M16" s="1" t="inlineStr"/>
       <c r="N16" s="1" t="inlineStr"/>
@@ -1514,7 +1474,7 @@
       <c r="P16" s="1" t="inlineStr"/>
       <c r="Q16" s="1" t="inlineStr">
         <is>
-          <t>L125: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | punctuation artifact: repeated periods :: duties simply caused prices of commod-f...â€¢.</t>
+          <t>L125: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | punctuation artifact: repeated periods :: duties simply caused prices of commod-f...•.</t>
         </is>
       </c>
       <c r="R16" s="1" t="inlineStr"/>
@@ -1553,11 +1513,7 @@
         </is>
       </c>
       <c r="J17" s="1" t="inlineStr"/>
-      <c r="K17" s="1" t="inlineStr">
-        <is>
-          <t>L406: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: should be thankful that we exist between week in the interests of East Flamboroâ€™</t>
-        </is>
-      </c>
+      <c r="K17" s="1" t="inlineStr"/>
       <c r="L17" s="1" t="inlineStr"/>
       <c r="M17" s="1" t="inlineStr"/>
       <c r="N17" s="1" t="inlineStr"/>
@@ -1588,11 +1544,7 @@
       <c r="H18" s="1" t="inlineStr"/>
       <c r="I18" s="1" t="inlineStr"/>
       <c r="J18" s="1" t="inlineStr"/>
-      <c r="K18" s="1" t="inlineStr">
-        <is>
-          <t>L408: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: the two extremesâ€”sunshine and rain | tions to the amount of $70. The fair this</t>
-        </is>
-      </c>
+      <c r="K18" s="1" t="inlineStr"/>
       <c r="L18" s="1" t="inlineStr"/>
       <c r="M18" s="1" t="inlineStr"/>
       <c r="N18" s="1" t="inlineStr"/>
@@ -1623,11 +1575,7 @@
       <c r="H19" s="1" t="inlineStr"/>
       <c r="I19" s="1" t="inlineStr"/>
       <c r="J19" s="1" t="inlineStr"/>
-      <c r="K19" s="1" t="inlineStr">
-        <is>
-          <t>L427: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER | suspicious token(s): 46summer (letter/digit mix) | candidate OCR token mismatch vs other OCR: "summer" vs "46summer" :: battle with 46summer diseaseâ€� must_â€” -</t>
-        </is>
-      </c>
+      <c r="K19" s="1" t="inlineStr"/>
       <c r="L19" s="1" t="inlineStr"/>
       <c r="M19" s="1" t="inlineStr"/>
       <c r="N19" s="1" t="inlineStr"/>
@@ -1658,11 +1606,7 @@
       <c r="H20" s="1" t="inlineStr"/>
       <c r="I20" s="1" t="inlineStr"/>
       <c r="J20" s="1" t="inlineStr"/>
-      <c r="K20" s="1" t="inlineStr">
-        <is>
-          <t>L429: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN | suspicious token(s): 1The (letter/digit mix) | localized OCR phrase divergence vs other OCR: "disease" vs "1The Fiftieth Day of Zachar s Fast" :: -1The Fiftieth Day of Zacharâ€™s Fast.</t>
-        </is>
-      </c>
+      <c r="K20" s="1" t="inlineStr"/>
       <c r="L20" s="1" t="inlineStr"/>
       <c r="M20" s="1" t="inlineStr"/>
       <c r="N20" s="1" t="inlineStr"/>
@@ -1693,11 +1637,7 @@
       <c r="H21" s="1" t="inlineStr"/>
       <c r="I21" s="1" t="inlineStr"/>
       <c r="J21" s="1" t="inlineStr"/>
-      <c r="K21" s="1" t="inlineStr">
-        <is>
-          <t>L440: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: But diluted cowâ€™s milk contains less fatty | three days. He has still strength enough</t>
-        </is>
-      </c>
+      <c r="K21" s="1" t="inlineStr"/>
       <c r="L21" s="1" t="inlineStr"/>
       <c r="M21" s="1" t="inlineStr"/>
       <c r="N21" s="1" t="inlineStr"/>
@@ -1728,11 +1668,7 @@
       <c r="H22" s="1" t="inlineStr"/>
       <c r="I22" s="1" t="inlineStr"/>
       <c r="J22" s="1" t="inlineStr"/>
-      <c r="K22" s="1" t="inlineStr">
-        <is>
-          <t>L445: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: these simple, yet necessary, precautions | Dr. Noyes says he found Zacharâ€™s pulse at</t>
-        </is>
-      </c>
+      <c r="K22" s="1" t="inlineStr"/>
       <c r="L22" s="1" t="inlineStr"/>
       <c r="M22" s="1" t="inlineStr"/>
       <c r="N22" s="1" t="inlineStr"/>
@@ -1763,11 +1699,7 @@
       <c r="H23" s="1" t="inlineStr"/>
       <c r="I23" s="1" t="inlineStr"/>
       <c r="J23" s="1" t="inlineStr"/>
-      <c r="K23" s="1" t="inlineStr">
-        <is>
-          <t>L456: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: of the Church of Scotland, gives various |__â€¢___________</t>
-        </is>
-      </c>
+      <c r="K23" s="1" t="inlineStr"/>
       <c r="L23" s="1" t="inlineStr"/>
       <c r="M23" s="1" t="inlineStr"/>
       <c r="N23" s="1" t="inlineStr"/>
@@ -1798,11 +1730,7 @@
       <c r="H24" s="1" t="inlineStr"/>
       <c r="I24" s="1" t="inlineStr"/>
       <c r="J24" s="1" t="inlineStr"/>
-      <c r="K24" s="1" t="inlineStr">
-        <is>
-          <t>L469: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: . â€” - - | Mr. David Thompson, M. P., father of the</t>
-        </is>
-      </c>
+      <c r="K24" s="1" t="inlineStr"/>
       <c r="L24" s="1" t="inlineStr"/>
       <c r="M24" s="1" t="inlineStr"/>
       <c r="N24" s="1" t="inlineStr"/>
@@ -1833,11 +1761,7 @@
       <c r="H25" s="1" t="inlineStr"/>
       <c r="I25" s="1" t="inlineStr"/>
       <c r="J25" s="1" t="inlineStr"/>
-      <c r="K25" s="1" t="inlineStr">
-        <is>
-          <t>L484: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: to have the opportunity of seeing and into Caledonia High School by theâ€™ Board</t>
-        </is>
-      </c>
+      <c r="K25" s="1" t="inlineStr"/>
       <c r="L25" s="1" t="inlineStr"/>
       <c r="M25" s="1" t="inlineStr"/>
       <c r="N25" s="1" t="inlineStr"/>
@@ -1868,11 +1792,7 @@
       <c r="H26" s="1" t="inlineStr"/>
       <c r="I26" s="1" t="inlineStr"/>
       <c r="J26" s="1" t="inlineStr"/>
-      <c r="K26" s="1" t="inlineStr">
-        <is>
-          <t>L494: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: other occupations tells the same storyâ€” execution ? It would goto the House of Com-</t>
-        </is>
-      </c>
+      <c r="K26" s="1" t="inlineStr"/>
       <c r="L26" s="1" t="inlineStr"/>
       <c r="M26" s="1" t="inlineStr"/>
       <c r="N26" s="1" t="inlineStr"/>
@@ -1903,11 +1823,7 @@
       <c r="H27" s="1" t="inlineStr"/>
       <c r="I27" s="1" t="inlineStr"/>
       <c r="J27" s="1" t="inlineStr"/>
-      <c r="K27" s="1" t="inlineStr">
-        <is>
-          <t>L511: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+02DC SMALL TILDE, U+2122 TRADE MARK SIGN :: boiled, called â€˜dufferyâ€™ or â€˜flummeryâ€™ orona s at the nomode of carrying</t>
-        </is>
-      </c>
+      <c r="K27" s="1" t="inlineStr"/>
       <c r="L27" s="1" t="inlineStr"/>
       <c r="M27" s="1" t="inlineStr"/>
       <c r="N27" s="1" t="inlineStr"/>
@@ -1938,11 +1854,7 @@
       <c r="H28" s="1" t="inlineStr"/>
       <c r="I28" s="1" t="inlineStr"/>
       <c r="J28" s="1" t="inlineStr"/>
-      <c r="K28" s="1" t="inlineStr">
-        <is>
-          <t>L524: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: the questionâ€”they never form the farmerâ€™s Council, should be so anxious to have their</t>
-        </is>
-      </c>
+      <c r="K28" s="1" t="inlineStr"/>
       <c r="L28" s="1" t="inlineStr"/>
       <c r="M28" s="1" t="inlineStr"/>
       <c r="N28" s="1" t="inlineStr"/>
@@ -1973,11 +1885,7 @@
       <c r="H29" s="1" t="inlineStr"/>
       <c r="I29" s="1" t="inlineStr"/>
       <c r="J29" s="1" t="inlineStr"/>
-      <c r="K29" s="1" t="inlineStr">
-        <is>
-          <t>L525: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+02DC SMALL TILDE :: food. Is not this a â€˜muzzling of the ox Lordships stretch their power beyond pre-</t>
-        </is>
-      </c>
+      <c r="K29" s="1" t="inlineStr"/>
       <c r="L29" s="1" t="inlineStr"/>
       <c r="M29" s="1" t="inlineStr"/>
       <c r="N29" s="1" t="inlineStr"/>
@@ -1985,7 +1893,7 @@
       <c r="P29" s="1" t="inlineStr"/>
       <c r="Q29" s="1" t="inlineStr">
         <is>
-          <t>L557: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: repeated periods :: campaign of 1880 in the United States,|.....................- ........â€”</t>
+          <t>L557: punctuation artifact: repeated periods :: campaign of 1880 in the United States,|.....................- ........—</t>
         </is>
       </c>
       <c r="R29" s="1" t="inlineStr"/>
@@ -2008,11 +1916,7 @@
       <c r="H30" s="1" t="inlineStr"/>
       <c r="I30" s="1" t="inlineStr"/>
       <c r="J30" s="1" t="inlineStr"/>
-      <c r="K30" s="1" t="inlineStr">
-        <is>
-          <t>L526: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+02DC SMALL TILDE :: which treadeth out the corn ?â€˜ The con- cedent in his own favor.</t>
-        </is>
-      </c>
+      <c r="K30" s="1" t="inlineStr"/>
       <c r="L30" s="1" t="inlineStr"/>
       <c r="M30" s="1" t="inlineStr"/>
       <c r="N30" s="1" t="inlineStr"/>
@@ -2043,11 +1947,7 @@
       <c r="H31" s="1" t="inlineStr"/>
       <c r="I31" s="1" t="inlineStr"/>
       <c r="J31" s="1" t="inlineStr"/>
-      <c r="K31" s="1" t="inlineStr">
-        <is>
-          <t>L533: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: them, having only one meal a day. Being â€žtrade will work for Reciprocity."</t>
-        </is>
-      </c>
+      <c r="K31" s="1" t="inlineStr"/>
       <c r="L31" s="1" t="inlineStr"/>
       <c r="M31" s="1" t="inlineStr"/>
       <c r="N31" s="1" t="inlineStr"/>
@@ -2055,7 +1955,7 @@
       <c r="P31" s="1" t="inlineStr"/>
       <c r="Q31" s="1" t="inlineStr">
         <is>
-          <t>L669: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: repeated periods; double/multiple hyphen | suspicious token(s): A1 (letter/digit mix) :: other words, his employment is lesssteady; I.. -------â€” ------A1, ,.</t>
+          <t>L669: punctuation artifact: repeated periods; double/multiple hyphen | suspicious token(s): A1 (letter/digit mix) :: other words, his employment is lesssteady; I.. -------— ------A1, ,.</t>
         </is>
       </c>
       <c r="R31" s="1" t="inlineStr"/>
@@ -2078,11 +1978,7 @@
       <c r="H32" s="1" t="inlineStr"/>
       <c r="I32" s="1" t="inlineStr"/>
       <c r="J32" s="1" t="inlineStr"/>
-      <c r="K32" s="1" t="inlineStr">
-        <is>
-          <t>L552: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: much for a comparison of two periods in on farmersâ€™ supplies that the farmers</t>
-        </is>
-      </c>
+      <c r="K32" s="1" t="inlineStr"/>
       <c r="L32" s="1" t="inlineStr"/>
       <c r="M32" s="1" t="inlineStr"/>
       <c r="N32" s="1" t="inlineStr"/>
@@ -2090,7 +1986,7 @@
       <c r="P32" s="1" t="inlineStr"/>
       <c r="Q32" s="1" t="inlineStr">
         <is>
-          <t>L734: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | punctuation artifact: double/multiple hyphen :: 2â€” ----------------â€¢â€”â€”â€” --------| employer, Mr. Alfred Nicholson, farmer, of</t>
+          <t>L734: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | punctuation artifact: double/multiple hyphen; hyphen/bullet debris :: 2— ----------------•——— --------| employer, Mr. Alfred Nicholson, farmer, of</t>
         </is>
       </c>
       <c r="R32" s="1" t="inlineStr"/>
@@ -2102,471 +1998,6 @@
       <c r="X32" s="1" t="inlineStr"/>
       <c r="Y32" s="1" t="inlineStr"/>
     </row>
-    <row r="33">
-      <c r="A33" s="1" t="inlineStr"/>
-      <c r="B33" s="1" t="inlineStr"/>
-      <c r="C33" s="1" t="inlineStr"/>
-      <c r="D33" s="1" t="inlineStr"/>
-      <c r="E33" s="1" t="inlineStr"/>
-      <c r="F33" s="1" t="inlineStr"/>
-      <c r="G33" s="1" t="inlineStr"/>
-      <c r="H33" s="1" t="inlineStr"/>
-      <c r="I33" s="1" t="inlineStr"/>
-      <c r="J33" s="1" t="inlineStr"/>
-      <c r="K33" s="1" t="inlineStr">
-        <is>
-          <t>L554: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: countries in the same period. According west. Isnâ€™t it time for the era of contra-</t>
-        </is>
-      </c>
-      <c r="L33" s="1" t="inlineStr"/>
-      <c r="M33" s="1" t="inlineStr"/>
-      <c r="N33" s="1" t="inlineStr"/>
-      <c r="O33" s="1" t="inlineStr"/>
-      <c r="P33" s="1" t="inlineStr"/>
-      <c r="Q33" s="1" t="inlineStr"/>
-      <c r="R33" s="1" t="inlineStr"/>
-      <c r="S33" s="1" t="inlineStr"/>
-      <c r="T33" s="1" t="inlineStr"/>
-      <c r="U33" s="1" t="inlineStr"/>
-      <c r="V33" s="1" t="inlineStr"/>
-      <c r="W33" s="1" t="inlineStr"/>
-      <c r="X33" s="1" t="inlineStr"/>
-      <c r="Y33" s="1" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="1" t="inlineStr"/>
-      <c r="B34" s="1" t="inlineStr"/>
-      <c r="C34" s="1" t="inlineStr"/>
-      <c r="D34" s="1" t="inlineStr"/>
-      <c r="E34" s="1" t="inlineStr"/>
-      <c r="F34" s="1" t="inlineStr"/>
-      <c r="G34" s="1" t="inlineStr"/>
-      <c r="H34" s="1" t="inlineStr"/>
-      <c r="I34" s="1" t="inlineStr"/>
-      <c r="J34" s="1" t="inlineStr"/>
-      <c r="K34" s="1" t="inlineStr">
-        <is>
-          <t>L557: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: repeated periods :: campaign of 1880 in the United States,|.....................- ........â€”</t>
-        </is>
-      </c>
-      <c r="L34" s="1" t="inlineStr"/>
-      <c r="M34" s="1" t="inlineStr"/>
-      <c r="N34" s="1" t="inlineStr"/>
-      <c r="O34" s="1" t="inlineStr"/>
-      <c r="P34" s="1" t="inlineStr"/>
-      <c r="Q34" s="1" t="inlineStr"/>
-      <c r="R34" s="1" t="inlineStr"/>
-      <c r="S34" s="1" t="inlineStr"/>
-      <c r="T34" s="1" t="inlineStr"/>
-      <c r="U34" s="1" t="inlineStr"/>
-      <c r="V34" s="1" t="inlineStr"/>
-      <c r="W34" s="1" t="inlineStr"/>
-      <c r="X34" s="1" t="inlineStr"/>
-      <c r="Y34" s="1" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="1" t="inlineStr"/>
-      <c r="B35" s="1" t="inlineStr"/>
-      <c r="C35" s="1" t="inlineStr"/>
-      <c r="D35" s="1" t="inlineStr"/>
-      <c r="E35" s="1" t="inlineStr"/>
-      <c r="F35" s="1" t="inlineStr"/>
-      <c r="G35" s="1" t="inlineStr"/>
-      <c r="H35" s="1" t="inlineStr"/>
-      <c r="I35" s="1" t="inlineStr"/>
-      <c r="J35" s="1" t="inlineStr"/>
-      <c r="K35" s="1" t="inlineStr">
-        <is>
-          <t>L669: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: repeated periods; double/multiple hyphen | suspicious token(s): A1 (letter/digit mix) :: other words, his employment is lesssteady; I.. -------â€” ------A1, ,.</t>
-        </is>
-      </c>
-      <c r="L35" s="1" t="inlineStr"/>
-      <c r="M35" s="1" t="inlineStr"/>
-      <c r="N35" s="1" t="inlineStr"/>
-      <c r="O35" s="1" t="inlineStr"/>
-      <c r="P35" s="1" t="inlineStr"/>
-      <c r="Q35" s="1" t="inlineStr"/>
-      <c r="R35" s="1" t="inlineStr"/>
-      <c r="S35" s="1" t="inlineStr"/>
-      <c r="T35" s="1" t="inlineStr"/>
-      <c r="U35" s="1" t="inlineStr"/>
-      <c r="V35" s="1" t="inlineStr"/>
-      <c r="W35" s="1" t="inlineStr"/>
-      <c r="X35" s="1" t="inlineStr"/>
-      <c r="Y35" s="1" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="1" t="inlineStr"/>
-      <c r="B36" s="1" t="inlineStr"/>
-      <c r="C36" s="1" t="inlineStr"/>
-      <c r="D36" s="1" t="inlineStr"/>
-      <c r="E36" s="1" t="inlineStr"/>
-      <c r="F36" s="1" t="inlineStr"/>
-      <c r="G36" s="1" t="inlineStr"/>
-      <c r="H36" s="1" t="inlineStr"/>
-      <c r="I36" s="1" t="inlineStr"/>
-      <c r="J36" s="1" t="inlineStr"/>
-      <c r="K36" s="1" t="inlineStr">
-        <is>
-          <t>L672: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: is true of other occupations. The cotton. Montague will not go on the two monthsâ€™</t>
-        </is>
-      </c>
-      <c r="L36" s="1" t="inlineStr"/>
-      <c r="M36" s="1" t="inlineStr"/>
-      <c r="N36" s="1" t="inlineStr"/>
-      <c r="O36" s="1" t="inlineStr"/>
-      <c r="P36" s="1" t="inlineStr"/>
-      <c r="Q36" s="1" t="inlineStr"/>
-      <c r="R36" s="1" t="inlineStr"/>
-      <c r="S36" s="1" t="inlineStr"/>
-      <c r="T36" s="1" t="inlineStr"/>
-      <c r="U36" s="1" t="inlineStr"/>
-      <c r="V36" s="1" t="inlineStr"/>
-      <c r="W36" s="1" t="inlineStr"/>
-      <c r="X36" s="1" t="inlineStr"/>
-      <c r="Y36" s="1" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="1" t="inlineStr"/>
-      <c r="B37" s="1" t="inlineStr"/>
-      <c r="C37" s="1" t="inlineStr"/>
-      <c r="D37" s="1" t="inlineStr"/>
-      <c r="E37" s="1" t="inlineStr"/>
-      <c r="F37" s="1" t="inlineStr"/>
-      <c r="G37" s="1" t="inlineStr"/>
-      <c r="H37" s="1" t="inlineStr"/>
-      <c r="I37" s="1" t="inlineStr"/>
-      <c r="J37" s="1" t="inlineStr"/>
-      <c r="K37" s="1" t="inlineStr">
-        <is>
-          <t>L709: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | line starts with punctuation glued to text :: -__________________â€”____________| Mahoney, a retired bookmaker, bet $20,000</t>
-        </is>
-      </c>
-      <c r="L37" s="1" t="inlineStr"/>
-      <c r="M37" s="1" t="inlineStr"/>
-      <c r="N37" s="1" t="inlineStr"/>
-      <c r="O37" s="1" t="inlineStr"/>
-      <c r="P37" s="1" t="inlineStr"/>
-      <c r="Q37" s="1" t="inlineStr"/>
-      <c r="R37" s="1" t="inlineStr"/>
-      <c r="S37" s="1" t="inlineStr"/>
-      <c r="T37" s="1" t="inlineStr"/>
-      <c r="U37" s="1" t="inlineStr"/>
-      <c r="V37" s="1" t="inlineStr"/>
-      <c r="W37" s="1" t="inlineStr"/>
-      <c r="X37" s="1" t="inlineStr"/>
-      <c r="Y37" s="1" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="1" t="inlineStr"/>
-      <c r="B38" s="1" t="inlineStr"/>
-      <c r="C38" s="1" t="inlineStr"/>
-      <c r="D38" s="1" t="inlineStr"/>
-      <c r="E38" s="1" t="inlineStr"/>
-      <c r="F38" s="1" t="inlineStr"/>
-      <c r="G38" s="1" t="inlineStr"/>
-      <c r="H38" s="1" t="inlineStr"/>
-      <c r="I38" s="1" t="inlineStr"/>
-      <c r="J38" s="1" t="inlineStr"/>
-      <c r="K38" s="1" t="inlineStr">
-        <is>
-          <t>L713: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN | line starts with punctuation glued to text | suspicious token(s): 1I (letter/digit mix) | localized OCR phrase divergence vs other OCR: "" vs "1I" :: -__1I Hoffman Club, on Clevelandâ€™s re-election,</t>
-        </is>
-      </c>
-      <c r="L38" s="1" t="inlineStr"/>
-      <c r="M38" s="1" t="inlineStr"/>
-      <c r="N38" s="1" t="inlineStr"/>
-      <c r="O38" s="1" t="inlineStr"/>
-      <c r="P38" s="1" t="inlineStr"/>
-      <c r="Q38" s="1" t="inlineStr"/>
-      <c r="R38" s="1" t="inlineStr"/>
-      <c r="S38" s="1" t="inlineStr"/>
-      <c r="T38" s="1" t="inlineStr"/>
-      <c r="U38" s="1" t="inlineStr"/>
-      <c r="V38" s="1" t="inlineStr"/>
-      <c r="W38" s="1" t="inlineStr"/>
-      <c r="X38" s="1" t="inlineStr"/>
-      <c r="Y38" s="1" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="1" t="inlineStr"/>
-      <c r="B39" s="1" t="inlineStr"/>
-      <c r="C39" s="1" t="inlineStr"/>
-      <c r="D39" s="1" t="inlineStr"/>
-      <c r="E39" s="1" t="inlineStr"/>
-      <c r="F39" s="1" t="inlineStr"/>
-      <c r="G39" s="1" t="inlineStr"/>
-      <c r="H39" s="1" t="inlineStr"/>
-      <c r="I39" s="1" t="inlineStr"/>
-      <c r="J39" s="1" t="inlineStr"/>
-      <c r="K39" s="1" t="inlineStr">
-        <is>
-          <t>L714: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN | suspicious token(s): wmNe (odd internal casing) :: by wmNe^Tis molested Mahoneyâ€™s forfeit in case of failure is fixed</t>
-        </is>
-      </c>
-      <c r="L39" s="1" t="inlineStr"/>
-      <c r="M39" s="1" t="inlineStr"/>
-      <c r="N39" s="1" t="inlineStr"/>
-      <c r="O39" s="1" t="inlineStr"/>
-      <c r="P39" s="1" t="inlineStr"/>
-      <c r="Q39" s="1" t="inlineStr"/>
-      <c r="R39" s="1" t="inlineStr"/>
-      <c r="S39" s="1" t="inlineStr"/>
-      <c r="T39" s="1" t="inlineStr"/>
-      <c r="U39" s="1" t="inlineStr"/>
-      <c r="V39" s="1" t="inlineStr"/>
-      <c r="W39" s="1" t="inlineStr"/>
-      <c r="X39" s="1" t="inlineStr"/>
-      <c r="Y39" s="1" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="1" t="inlineStr"/>
-      <c r="B40" s="1" t="inlineStr"/>
-      <c r="C40" s="1" t="inlineStr"/>
-      <c r="D40" s="1" t="inlineStr"/>
-      <c r="E40" s="1" t="inlineStr"/>
-      <c r="F40" s="1" t="inlineStr"/>
-      <c r="G40" s="1" t="inlineStr"/>
-      <c r="H40" s="1" t="inlineStr"/>
-      <c r="I40" s="1" t="inlineStr"/>
-      <c r="J40" s="1" t="inlineStr"/>
-      <c r="K40" s="1" t="inlineStr">
-        <is>
-          <t>L715: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: of the Police Court with having stolen a at $5,000 and Huntoonâ€™s at $2,500.</t>
-        </is>
-      </c>
-      <c r="L40" s="1" t="inlineStr"/>
-      <c r="M40" s="1" t="inlineStr"/>
-      <c r="N40" s="1" t="inlineStr"/>
-      <c r="O40" s="1" t="inlineStr"/>
-      <c r="P40" s="1" t="inlineStr"/>
-      <c r="Q40" s="1" t="inlineStr"/>
-      <c r="R40" s="1" t="inlineStr"/>
-      <c r="S40" s="1" t="inlineStr"/>
-      <c r="T40" s="1" t="inlineStr"/>
-      <c r="U40" s="1" t="inlineStr"/>
-      <c r="V40" s="1" t="inlineStr"/>
-      <c r="W40" s="1" t="inlineStr"/>
-      <c r="X40" s="1" t="inlineStr"/>
-      <c r="Y40" s="1" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="1" t="inlineStr"/>
-      <c r="B41" s="1" t="inlineStr"/>
-      <c r="C41" s="1" t="inlineStr"/>
-      <c r="D41" s="1" t="inlineStr"/>
-      <c r="E41" s="1" t="inlineStr"/>
-      <c r="F41" s="1" t="inlineStr"/>
-      <c r="G41" s="1" t="inlineStr"/>
-      <c r="H41" s="1" t="inlineStr"/>
-      <c r="I41" s="1" t="inlineStr"/>
-      <c r="J41" s="1" t="inlineStr"/>
-      <c r="K41" s="1" t="inlineStr">
-        <is>
-          <t>L717: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: who iven n neater, but keeps his horse â€”The girl Sarah Osborne, of Waterford,</t>
-        </is>
-      </c>
-      <c r="L41" s="1" t="inlineStr"/>
-      <c r="M41" s="1" t="inlineStr"/>
-      <c r="N41" s="1" t="inlineStr"/>
-      <c r="O41" s="1" t="inlineStr"/>
-      <c r="P41" s="1" t="inlineStr"/>
-      <c r="Q41" s="1" t="inlineStr"/>
-      <c r="R41" s="1" t="inlineStr"/>
-      <c r="S41" s="1" t="inlineStr"/>
-      <c r="T41" s="1" t="inlineStr"/>
-      <c r="U41" s="1" t="inlineStr"/>
-      <c r="V41" s="1" t="inlineStr"/>
-      <c r="W41" s="1" t="inlineStr"/>
-      <c r="X41" s="1" t="inlineStr"/>
-      <c r="Y41" s="1" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="1" t="inlineStr"/>
-      <c r="B42" s="1" t="inlineStr"/>
-      <c r="C42" s="1" t="inlineStr"/>
-      <c r="D42" s="1" t="inlineStr"/>
-      <c r="E42" s="1" t="inlineStr"/>
-      <c r="F42" s="1" t="inlineStr"/>
-      <c r="G42" s="1" t="inlineStr"/>
-      <c r="H42" s="1" t="inlineStr"/>
-      <c r="I42" s="1" t="inlineStr"/>
-      <c r="J42" s="1" t="inlineStr"/>
-      <c r="K42" s="1" t="inlineStr">
-        <is>
-          <t>L724: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: About 11 o'clock he found it in McNeilâ€™s went as far as Mount Pleasant and then</t>
-        </is>
-      </c>
-      <c r="L42" s="1" t="inlineStr"/>
-      <c r="M42" s="1" t="inlineStr"/>
-      <c r="N42" s="1" t="inlineStr"/>
-      <c r="O42" s="1" t="inlineStr"/>
-      <c r="P42" s="1" t="inlineStr"/>
-      <c r="Q42" s="1" t="inlineStr"/>
-      <c r="R42" s="1" t="inlineStr"/>
-      <c r="S42" s="1" t="inlineStr"/>
-      <c r="T42" s="1" t="inlineStr"/>
-      <c r="U42" s="1" t="inlineStr"/>
-      <c r="V42" s="1" t="inlineStr"/>
-      <c r="W42" s="1" t="inlineStr"/>
-      <c r="X42" s="1" t="inlineStr"/>
-      <c r="Y42" s="1" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="1" t="inlineStr"/>
-      <c r="B43" s="1" t="inlineStr"/>
-      <c r="C43" s="1" t="inlineStr"/>
-      <c r="D43" s="1" t="inlineStr"/>
-      <c r="E43" s="1" t="inlineStr"/>
-      <c r="F43" s="1" t="inlineStr"/>
-      <c r="G43" s="1" t="inlineStr"/>
-      <c r="H43" s="1" t="inlineStr"/>
-      <c r="I43" s="1" t="inlineStr"/>
-      <c r="J43" s="1" t="inlineStr"/>
-      <c r="K43" s="1" t="inlineStr">
-        <is>
-          <t>L731: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: trate advised him to stick to the truth in â€”James Walton, the lad who pleaded</t>
-        </is>
-      </c>
-      <c r="L43" s="1" t="inlineStr"/>
-      <c r="M43" s="1" t="inlineStr"/>
-      <c r="N43" s="1" t="inlineStr"/>
-      <c r="O43" s="1" t="inlineStr"/>
-      <c r="P43" s="1" t="inlineStr"/>
-      <c r="Q43" s="1" t="inlineStr"/>
-      <c r="R43" s="1" t="inlineStr"/>
-      <c r="S43" s="1" t="inlineStr"/>
-      <c r="T43" s="1" t="inlineStr"/>
-      <c r="U43" s="1" t="inlineStr"/>
-      <c r="V43" s="1" t="inlineStr"/>
-      <c r="W43" s="1" t="inlineStr"/>
-      <c r="X43" s="1" t="inlineStr"/>
-      <c r="Y43" s="1" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="1" t="inlineStr"/>
-      <c r="B44" s="1" t="inlineStr"/>
-      <c r="C44" s="1" t="inlineStr"/>
-      <c r="D44" s="1" t="inlineStr"/>
-      <c r="E44" s="1" t="inlineStr"/>
-      <c r="F44" s="1" t="inlineStr"/>
-      <c r="G44" s="1" t="inlineStr"/>
-      <c r="H44" s="1" t="inlineStr"/>
-      <c r="I44" s="1" t="inlineStr"/>
-      <c r="J44" s="1" t="inlineStr"/>
-      <c r="K44" s="1" t="inlineStr">
-        <is>
-          <t>L734: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | punctuation artifact: double/multiple hyphen :: 2â€” ----------------â€¢â€”â€”â€” --------| employer, Mr. Alfred Nicholson, farmer, of</t>
-        </is>
-      </c>
-      <c r="L44" s="1" t="inlineStr"/>
-      <c r="M44" s="1" t="inlineStr"/>
-      <c r="N44" s="1" t="inlineStr"/>
-      <c r="O44" s="1" t="inlineStr"/>
-      <c r="P44" s="1" t="inlineStr"/>
-      <c r="Q44" s="1" t="inlineStr"/>
-      <c r="R44" s="1" t="inlineStr"/>
-      <c r="S44" s="1" t="inlineStr"/>
-      <c r="T44" s="1" t="inlineStr"/>
-      <c r="U44" s="1" t="inlineStr"/>
-      <c r="V44" s="1" t="inlineStr"/>
-      <c r="W44" s="1" t="inlineStr"/>
-      <c r="X44" s="1" t="inlineStr"/>
-      <c r="Y44" s="1" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="1" t="inlineStr"/>
-      <c r="B45" s="1" t="inlineStr"/>
-      <c r="C45" s="1" t="inlineStr"/>
-      <c r="D45" s="1" t="inlineStr"/>
-      <c r="E45" s="1" t="inlineStr"/>
-      <c r="F45" s="1" t="inlineStr"/>
-      <c r="G45" s="1" t="inlineStr"/>
-      <c r="H45" s="1" t="inlineStr"/>
-      <c r="I45" s="1" t="inlineStr"/>
-      <c r="J45" s="1" t="inlineStr"/>
-      <c r="K45" s="1" t="inlineStr">
-        <is>
-          <t>L736: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€”A golden wedding is rare enough, but | Elfrida, came up for sentencebeforethe</t>
-        </is>
-      </c>
-      <c r="L45" s="1" t="inlineStr"/>
-      <c r="M45" s="1" t="inlineStr"/>
-      <c r="N45" s="1" t="inlineStr"/>
-      <c r="O45" s="1" t="inlineStr"/>
-      <c r="P45" s="1" t="inlineStr"/>
-      <c r="Q45" s="1" t="inlineStr"/>
-      <c r="R45" s="1" t="inlineStr"/>
-      <c r="S45" s="1" t="inlineStr"/>
-      <c r="T45" s="1" t="inlineStr"/>
-      <c r="U45" s="1" t="inlineStr"/>
-      <c r="V45" s="1" t="inlineStr"/>
-      <c r="W45" s="1" t="inlineStr"/>
-      <c r="X45" s="1" t="inlineStr"/>
-      <c r="Y45" s="1" t="inlineStr"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="1" t="inlineStr"/>
-      <c r="B46" s="1" t="inlineStr"/>
-      <c r="C46" s="1" t="inlineStr"/>
-      <c r="D46" s="1" t="inlineStr"/>
-      <c r="E46" s="1" t="inlineStr"/>
-      <c r="F46" s="1" t="inlineStr"/>
-      <c r="G46" s="1" t="inlineStr"/>
-      <c r="H46" s="1" t="inlineStr"/>
-      <c r="I46" s="1" t="inlineStr"/>
-      <c r="J46" s="1" t="inlineStr"/>
-      <c r="K46" s="1" t="inlineStr">
-        <is>
-          <t>L786: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: the Government, though Mr. Muirâ€™s inti-</t>
-        </is>
-      </c>
-      <c r="L46" s="1" t="inlineStr"/>
-      <c r="M46" s="1" t="inlineStr"/>
-      <c r="N46" s="1" t="inlineStr"/>
-      <c r="O46" s="1" t="inlineStr"/>
-      <c r="P46" s="1" t="inlineStr"/>
-      <c r="Q46" s="1" t="inlineStr"/>
-      <c r="R46" s="1" t="inlineStr"/>
-      <c r="S46" s="1" t="inlineStr"/>
-      <c r="T46" s="1" t="inlineStr"/>
-      <c r="U46" s="1" t="inlineStr"/>
-      <c r="V46" s="1" t="inlineStr"/>
-      <c r="W46" s="1" t="inlineStr"/>
-      <c r="X46" s="1" t="inlineStr"/>
-      <c r="Y46" s="1" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="1" t="inlineStr"/>
-      <c r="B47" s="1" t="inlineStr"/>
-      <c r="C47" s="1" t="inlineStr"/>
-      <c r="D47" s="1" t="inlineStr"/>
-      <c r="E47" s="1" t="inlineStr"/>
-      <c r="F47" s="1" t="inlineStr"/>
-      <c r="G47" s="1" t="inlineStr"/>
-      <c r="H47" s="1" t="inlineStr"/>
-      <c r="I47" s="1" t="inlineStr"/>
-      <c r="J47" s="1" t="inlineStr"/>
-      <c r="K47" s="1" t="inlineStr">
-        <is>
-          <t>L788: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: of a â€œjudicial mind." The proof of the</t>
-        </is>
-      </c>
-      <c r="L47" s="1" t="inlineStr"/>
-      <c r="M47" s="1" t="inlineStr"/>
-      <c r="N47" s="1" t="inlineStr"/>
-      <c r="O47" s="1" t="inlineStr"/>
-      <c r="P47" s="1" t="inlineStr"/>
-      <c r="Q47" s="1" t="inlineStr"/>
-      <c r="R47" s="1" t="inlineStr"/>
-      <c r="S47" s="1" t="inlineStr"/>
-      <c r="T47" s="1" t="inlineStr"/>
-      <c r="U47" s="1" t="inlineStr"/>
-      <c r="V47" s="1" t="inlineStr"/>
-      <c r="W47" s="1" t="inlineStr"/>
-      <c r="X47" s="1" t="inlineStr"/>
-      <c r="Y47" s="1" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
